--- a/excel/read_dethi.xlsx
+++ b/excel/read_dethi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\VISUAL\my-project\QuanLyQuiz\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74695871-2475-4BCD-9FA1-CF537B7E9CA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36D975D2-FC39-4604-95A0-6F070290CA9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{1DDF21FF-ACF5-491C-A4EC-DBC3D782DD3D}"/>
   </bookViews>
@@ -447,8 +447,9 @@
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="22.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.36328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="8.7265625" style="1"/>
+    <col min="4" max="4" width="9.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.81640625" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">

--- a/excel/read_dethi.xlsx
+++ b/excel/read_dethi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\VISUAL\my-project\QuanLyQuiz\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36D975D2-FC39-4604-95A0-6F070290CA9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA62580D-0666-4449-96EE-074DE768171D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{1DDF21FF-ACF5-491C-A4EC-DBC3D782DD3D}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
   <si>
     <t>Tên đề</t>
   </si>
@@ -50,16 +50,19 @@
     <t>Thời gian</t>
   </si>
   <si>
-    <t>Người tạo</t>
-  </si>
-  <si>
-    <t>Admin</t>
-  </si>
-  <si>
     <t>Đề kiểm tra 15 phút Java</t>
   </si>
   <si>
     <t>Đề cuối kỳ 2 Java</t>
+  </si>
+  <si>
+    <t>Thi Giữa Kỳ 1</t>
+  </si>
+  <si>
+    <t>Kiểm tra 15 phút</t>
+  </si>
+  <si>
+    <t>Lập trình Java</t>
   </si>
 </sst>
 </file>
@@ -447,12 +450,13 @@
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="22.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="8.7265625" style="1"/>
+    <col min="2" max="2" width="15.08984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.90625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.36328125" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.81640625" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -465,42 +469,33 @@
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>4</v>
       </c>
+      <c r="B2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="1">
+        <v>60</v>
+      </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="1">
-        <v>2</v>
-      </c>
-      <c r="C2" s="1">
-        <v>1</v>
-      </c>
-      <c r="D2" s="1">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="1">
         <v>15</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="1">
-        <v>3</v>
-      </c>
-      <c r="C3" s="1">
-        <v>1</v>
-      </c>
-      <c r="D3" s="1">
-        <v>60</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
